--- a/Referencias/tbl_KMM_Contas.xlsx
+++ b/Referencias/tbl_KMM_Contas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nstechcloud.sharepoint.com/sites/financial_reporting/Documentos Compartilhados/FPA_DW/Datalake_readFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="8_{6EB7E3AC-58EB-453C-94D3-D1E0C4DB185F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{076D65ED-A920-4818-B89F-DE85F5575983}"/>
+  <xr:revisionPtr revIDLastSave="245" documentId="8_{6EB7E3AC-58EB-453C-94D3-D1E0C4DB185F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{511A4E68-115A-4280-A014-1594771D639E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{16554D6A-23AB-43A0-89E6-5F56AE2445FC}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="dContas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dContas!$A$1:$I$631</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dContas!$A$1:$I$636</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4329" uniqueCount="2360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4339" uniqueCount="2368">
   <si>
     <t>ContaContabil</t>
   </si>
@@ -7119,12 +7119,36 @@
   </si>
   <si>
     <t>IVA</t>
+  </si>
+  <si>
+    <t>REVERSAO DE PROVISAO DE CONTINGENCIA TRABALHISTA</t>
+  </si>
+  <si>
+    <t>(NT-PIS/COFINS) ANTECIPAÇÃO RECEITA (-)</t>
+  </si>
+  <si>
+    <t>4.7.03.004.009</t>
+  </si>
+  <si>
+    <t>GASTOS COM IA</t>
+  </si>
+  <si>
+    <t>ANTECIPAÇÃO DE RECEITA (NT-PIS/COFINS)</t>
+  </si>
+  <si>
+    <t>4.7.03.001.036</t>
+  </si>
+  <si>
+    <t>REMUNERAÇÃO BASEADA EM AÇÕES</t>
+  </si>
+  <si>
+    <t>Comissões</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -7174,17 +7198,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{3B6E8DFF-3B20-49CB-BD3E-7FB599A6D1D8}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -7194,6 +7223,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7513,7 +7546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CDEB827-A2B7-42BE-B86F-19DD993B7A8F}">
-  <dimension ref="A1:I631"/>
+  <dimension ref="A1:I636"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -7556,7 +7589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -7583,7 +7616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -7610,7 +7643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -7637,7 +7670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -7664,7 +7697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -7691,7 +7724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -7718,7 +7751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -7745,7 +7778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -7772,7 +7805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -7799,7 +7832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -7826,7 +7859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -7853,7 +7886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -7880,7 +7913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -7907,7 +7940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -7934,7 +7967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -7961,7 +7994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>71</v>
       </c>
@@ -7988,7 +8021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>75</v>
       </c>
@@ -8015,7 +8048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>79</v>
       </c>
@@ -8042,7 +8075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>83</v>
       </c>
@@ -8072,7 +8105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>88</v>
       </c>
@@ -8099,7 +8132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -8126,7 +8159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>96</v>
       </c>
@@ -8153,7 +8186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>100</v>
       </c>
@@ -8180,7 +8213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>104</v>
       </c>
@@ -8207,7 +8240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>108</v>
       </c>
@@ -8234,7 +8267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>112</v>
       </c>
@@ -8261,7 +8294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>116</v>
       </c>
@@ -8288,7 +8321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>120</v>
       </c>
@@ -8315,7 +8348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>124</v>
       </c>
@@ -8342,7 +8375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>128</v>
       </c>
@@ -8369,7 +8402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>132</v>
       </c>
@@ -8396,7 +8429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>136</v>
       </c>
@@ -8423,7 +8456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>140</v>
       </c>
@@ -8450,7 +8483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>144</v>
       </c>
@@ -8477,7 +8510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>147</v>
       </c>
@@ -8504,7 +8537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>151</v>
       </c>
@@ -8534,7 +8567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>157</v>
       </c>
@@ -8564,7 +8597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>163</v>
       </c>
@@ -8591,7 +8624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>167</v>
       </c>
@@ -8618,7 +8651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>171</v>
       </c>
@@ -8645,7 +8678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>175</v>
       </c>
@@ -8675,7 +8708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>180</v>
       </c>
@@ -8705,7 +8738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>184</v>
       </c>
@@ -8732,7 +8765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>188</v>
       </c>
@@ -8759,7 +8792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>193</v>
       </c>
@@ -8789,7 +8822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>197</v>
       </c>
@@ -8816,7 +8849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>202</v>
       </c>
@@ -8843,7 +8876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>206</v>
       </c>
@@ -8873,7 +8906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>210</v>
       </c>
@@ -8903,7 +8936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>215</v>
       </c>
@@ -8933,7 +8966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>220</v>
       </c>
@@ -8963,7 +8996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>225</v>
       </c>
@@ -8993,7 +9026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>230</v>
       </c>
@@ -9020,7 +9053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>234</v>
       </c>
@@ -9047,7 +9080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>238</v>
       </c>
@@ -9074,7 +9107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>242</v>
       </c>
@@ -9101,7 +9134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>248</v>
       </c>
@@ -9131,7 +9164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>252</v>
       </c>
@@ -9161,7 +9194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>256</v>
       </c>
@@ -9191,7 +9224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>260</v>
       </c>
@@ -9221,7 +9254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>264</v>
       </c>
@@ -9248,7 +9281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>268</v>
       </c>
@@ -9278,7 +9311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>272</v>
       </c>
@@ -9308,7 +9341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>276</v>
       </c>
@@ -9338,7 +9371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>280</v>
       </c>
@@ -9368,7 +9401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>284</v>
       </c>
@@ -9398,7 +9431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>288</v>
       </c>
@@ -9425,7 +9458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>291</v>
       </c>
@@ -9455,7 +9488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>295</v>
       </c>
@@ -9482,7 +9515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>298</v>
       </c>
@@ -9509,7 +9542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>302</v>
       </c>
@@ -9539,7 +9572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>306</v>
       </c>
@@ -9566,7 +9599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>310</v>
       </c>
@@ -9596,7 +9629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>313</v>
       </c>
@@ -9626,7 +9659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>317</v>
       </c>
@@ -9656,7 +9689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>320</v>
       </c>
@@ -9686,7 +9719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>324</v>
       </c>
@@ -9713,7 +9746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>328</v>
       </c>
@@ -9740,7 +9773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>333</v>
       </c>
@@ -9770,7 +9803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>338</v>
       </c>
@@ -9797,7 +9830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>342</v>
       </c>
@@ -9827,7 +9860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>346</v>
       </c>
@@ -9857,7 +9890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>351</v>
       </c>
@@ -9887,7 +9920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>355</v>
       </c>
@@ -9917,7 +9950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>359</v>
       </c>
@@ -9944,7 +9977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>363</v>
       </c>
@@ -9974,7 +10007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>369</v>
       </c>
@@ -10004,7 +10037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>373</v>
       </c>
@@ -10034,7 +10067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>379</v>
       </c>
@@ -10064,7 +10097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>386</v>
       </c>
@@ -10091,7 +10124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>390</v>
       </c>
@@ -10121,7 +10154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>395</v>
       </c>
@@ -10151,7 +10184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>399</v>
       </c>
@@ -10181,7 +10214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>404</v>
       </c>
@@ -10211,7 +10244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>409</v>
       </c>
@@ -10241,7 +10274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>413</v>
       </c>
@@ -10271,7 +10304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>418</v>
       </c>
@@ -10301,7 +10334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>423</v>
       </c>
@@ -10331,7 +10364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>427</v>
       </c>
@@ -10361,7 +10394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>431</v>
       </c>
@@ -10391,7 +10424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>435</v>
       </c>
@@ -10421,7 +10454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>4703001021</v>
       </c>
@@ -10451,7 +10484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>439</v>
       </c>
@@ -10481,7 +10514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>443</v>
       </c>
@@ -10511,7 +10544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>447</v>
       </c>
@@ -10541,7 +10574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>451</v>
       </c>
@@ -10568,7 +10601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>455</v>
       </c>
@@ -10595,7 +10628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>459</v>
       </c>
@@ -10622,7 +10655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>462</v>
       </c>
@@ -10649,7 +10682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>466</v>
       </c>
@@ -10679,7 +10712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>470</v>
       </c>
@@ -10709,7 +10742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>474</v>
       </c>
@@ -10739,7 +10772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>480</v>
       </c>
@@ -10766,7 +10799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>484</v>
       </c>
@@ -10793,7 +10826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>487</v>
       </c>
@@ -10820,7 +10853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>491</v>
       </c>
@@ -10847,7 +10880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>495</v>
       </c>
@@ -10874,7 +10907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>499</v>
       </c>
@@ -10901,7 +10934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>503</v>
       </c>
@@ -10928,7 +10961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>507</v>
       </c>
@@ -10955,7 +10988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>511</v>
       </c>
@@ -10982,7 +11015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>514</v>
       </c>
@@ -11009,7 +11042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>518</v>
       </c>
@@ -11039,7 +11072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>523</v>
       </c>
@@ -11069,7 +11102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>526</v>
       </c>
@@ -11099,7 +11132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>530</v>
       </c>
@@ -11126,7 +11159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>533</v>
       </c>
@@ -11153,7 +11186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>536</v>
       </c>
@@ -11180,7 +11213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>539</v>
       </c>
@@ -11207,7 +11240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>542</v>
       </c>
@@ -11234,7 +11267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>546</v>
       </c>
@@ -11261,7 +11294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>550</v>
       </c>
@@ -11288,7 +11321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>554</v>
       </c>
@@ -11315,7 +11348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>558</v>
       </c>
@@ -11342,7 +11375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>562</v>
       </c>
@@ -11369,7 +11402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>566</v>
       </c>
@@ -11396,7 +11429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>570</v>
       </c>
@@ -11423,7 +11456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>574</v>
       </c>
@@ -11450,7 +11483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>578</v>
       </c>
@@ -11477,7 +11510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>582</v>
       </c>
@@ -11504,7 +11537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>586</v>
       </c>
@@ -11531,7 +11564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>590</v>
       </c>
@@ -11558,7 +11591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>594</v>
       </c>
@@ -11585,7 +11618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>598</v>
       </c>
@@ -11612,7 +11645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>602</v>
       </c>
@@ -11639,7 +11672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>606</v>
       </c>
@@ -11666,7 +11699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>610</v>
       </c>
@@ -11693,7 +11726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>614</v>
       </c>
@@ -11720,7 +11753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>618</v>
       </c>
@@ -11747,7 +11780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>622</v>
       </c>
@@ -11760,8 +11793,9 @@
       <c r="D151" t="s">
         <v>625</v>
       </c>
-      <c r="E151" t="s">
-        <v>626</v>
+      <c r="E151" t="str">
+        <f>G151</f>
+        <v>Benfeitorias e outros</v>
       </c>
       <c r="F151" t="s">
         <v>626</v>
@@ -11774,7 +11808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>628</v>
       </c>
@@ -11804,7 +11838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>632</v>
       </c>
@@ -11831,7 +11865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>636</v>
       </c>
@@ -11858,7 +11892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>640</v>
       </c>
@@ -11885,7 +11919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>644</v>
       </c>
@@ -11945,7 +11979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>654</v>
       </c>
@@ -11975,7 +12009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>659</v>
       </c>
@@ -12005,7 +12039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>663</v>
       </c>
@@ -12032,7 +12066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>667</v>
       </c>
@@ -12059,7 +12093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>671</v>
       </c>
@@ -12086,7 +12120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>674</v>
       </c>
@@ -12113,7 +12147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>678</v>
       </c>
@@ -12143,7 +12177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>683</v>
       </c>
@@ -12173,7 +12207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>687</v>
       </c>
@@ -12200,7 +12234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>691</v>
       </c>
@@ -12230,7 +12264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>693</v>
       </c>
@@ -12257,7 +12291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>697</v>
       </c>
@@ -12284,7 +12318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>701</v>
       </c>
@@ -12314,7 +12348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>706</v>
       </c>
@@ -12344,7 +12378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>710</v>
       </c>
@@ -12371,7 +12405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>714</v>
       </c>
@@ -12398,7 +12432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>718</v>
       </c>
@@ -12425,7 +12459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>722</v>
       </c>
@@ -12452,7 +12486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>726</v>
       </c>
@@ -12482,7 +12516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>730</v>
       </c>
@@ -12509,7 +12543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>734</v>
       </c>
@@ -12539,7 +12573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>738</v>
       </c>
@@ -12566,7 +12600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>741</v>
       </c>
@@ -12596,7 +12630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>745</v>
       </c>
@@ -12623,7 +12657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>748</v>
       </c>
@@ -12653,7 +12687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>752</v>
       </c>
@@ -12683,7 +12717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>757</v>
       </c>
@@ -12710,7 +12744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>761</v>
       </c>
@@ -12740,7 +12774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>764</v>
       </c>
@@ -12770,7 +12804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>768</v>
       </c>
@@ -12790,7 +12824,7 @@
         <v>384</v>
       </c>
       <c r="G187" t="s">
-        <v>653</v>
+        <v>2367</v>
       </c>
       <c r="H187">
         <f t="shared" si="2"/>
@@ -12800,7 +12834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>772</v>
       </c>
@@ -12827,7 +12861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>776</v>
       </c>
@@ -12857,7 +12891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>781</v>
       </c>
@@ -12871,7 +12905,7 @@
         <v>784</v>
       </c>
       <c r="E190" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="F190" t="s">
         <v>377</v>
@@ -12887,7 +12921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>787</v>
       </c>
@@ -12917,7 +12951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>792</v>
       </c>
@@ -12931,7 +12965,7 @@
         <v>790</v>
       </c>
       <c r="E192" t="s">
-        <v>229</v>
+        <v>791</v>
       </c>
       <c r="F192" t="s">
         <v>377</v>
@@ -12947,7 +12981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>795</v>
       </c>
@@ -12977,7 +13011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>799</v>
       </c>
@@ -12991,7 +13025,7 @@
         <v>802</v>
       </c>
       <c r="E194" t="s">
-        <v>229</v>
+        <v>791</v>
       </c>
       <c r="F194" t="s">
         <v>246</v>
@@ -13007,7 +13041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>803</v>
       </c>
@@ -13037,7 +13071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>807</v>
       </c>
@@ -13067,7 +13101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>810</v>
       </c>
@@ -13097,7 +13131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>813</v>
       </c>
@@ -13127,7 +13161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>816</v>
       </c>
@@ -13157,7 +13191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>819</v>
       </c>
@@ -13171,7 +13205,7 @@
         <v>806</v>
       </c>
       <c r="E200" t="s">
-        <v>229</v>
+        <v>791</v>
       </c>
       <c r="F200" t="s">
         <v>377</v>
@@ -13187,7 +13221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>822</v>
       </c>
@@ -13217,7 +13251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>825</v>
       </c>
@@ -13231,7 +13265,7 @@
         <v>828</v>
       </c>
       <c r="E202" t="s">
-        <v>383</v>
+        <v>791</v>
       </c>
       <c r="F202" t="s">
         <v>384</v>
@@ -13247,7 +13281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>829</v>
       </c>
@@ -13261,7 +13295,7 @@
         <v>832</v>
       </c>
       <c r="E203" t="s">
-        <v>229</v>
+        <v>791</v>
       </c>
       <c r="F203" t="s">
         <v>246</v>
@@ -13277,7 +13311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>833</v>
       </c>
@@ -13291,7 +13325,7 @@
         <v>836</v>
       </c>
       <c r="E204" t="s">
-        <v>229</v>
+        <v>791</v>
       </c>
       <c r="F204" t="s">
         <v>837</v>
@@ -13307,7 +13341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>838</v>
       </c>
@@ -13337,7 +13371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>842</v>
       </c>
@@ -13367,7 +13401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>846</v>
       </c>
@@ -13397,7 +13431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>850</v>
       </c>
@@ -13411,7 +13445,7 @@
         <v>849</v>
       </c>
       <c r="E208" t="s">
-        <v>229</v>
+        <v>791</v>
       </c>
       <c r="F208" t="s">
         <v>377</v>
@@ -13427,7 +13461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>853</v>
       </c>
@@ -13457,7 +13491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>857</v>
       </c>
@@ -13471,7 +13505,7 @@
         <v>856</v>
       </c>
       <c r="E210" t="s">
-        <v>229</v>
+        <v>791</v>
       </c>
       <c r="F210" t="s">
         <v>377</v>
@@ -13487,7 +13521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>860</v>
       </c>
@@ -13517,7 +13551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>864</v>
       </c>
@@ -13531,7 +13565,7 @@
         <v>863</v>
       </c>
       <c r="E212" t="s">
-        <v>229</v>
+        <v>791</v>
       </c>
       <c r="F212" t="s">
         <v>377</v>
@@ -13547,7 +13581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>867</v>
       </c>
@@ -13577,7 +13611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>872</v>
       </c>
@@ -13607,7 +13641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>874</v>
       </c>
@@ -13637,7 +13671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>876</v>
       </c>
@@ -13667,7 +13701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>880</v>
       </c>
@@ -13694,7 +13728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>884</v>
       </c>
@@ -13721,7 +13755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>888</v>
       </c>
@@ -13748,7 +13782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>894</v>
       </c>
@@ -13778,7 +13812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>898</v>
       </c>
@@ -13805,7 +13839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>902</v>
       </c>
@@ -13832,7 +13866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>906</v>
       </c>
@@ -13859,7 +13893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>910</v>
       </c>
@@ -13889,7 +13923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>914</v>
       </c>
@@ -13919,7 +13953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>917</v>
       </c>
@@ -13949,7 +13983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>920</v>
       </c>
@@ -13979,7 +14013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>923</v>
       </c>
@@ -14009,7 +14043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>926</v>
       </c>
@@ -14039,7 +14073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>929</v>
       </c>
@@ -14066,7 +14100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>932</v>
       </c>
@@ -14096,7 +14130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>936</v>
       </c>
@@ -14123,7 +14157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>940</v>
       </c>
@@ -14150,7 +14184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>944</v>
       </c>
@@ -14180,7 +14214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>949</v>
       </c>
@@ -14210,7 +14244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>953</v>
       </c>
@@ -14240,7 +14274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>955</v>
       </c>
@@ -14270,7 +14304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>958</v>
       </c>
@@ -14297,7 +14331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>959</v>
       </c>
@@ -14327,7 +14361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>963</v>
       </c>
@@ -14357,7 +14391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>965</v>
       </c>
@@ -14387,7 +14421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>966</v>
       </c>
@@ -14417,7 +14451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>970</v>
       </c>
@@ -14444,7 +14478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>973</v>
       </c>
@@ -14471,7 +14505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>977</v>
       </c>
@@ -14501,7 +14535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>981</v>
       </c>
@@ -14531,7 +14565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>985</v>
       </c>
@@ -14561,7 +14595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>990</v>
       </c>
@@ -14591,7 +14625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>995</v>
       </c>
@@ -14618,7 +14652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>999</v>
       </c>
@@ -14645,7 +14679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>1003</v>
       </c>
@@ -14675,7 +14709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1007</v>
       </c>
@@ -14705,7 +14739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>1011</v>
       </c>
@@ -14735,7 +14769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>1015</v>
       </c>
@@ -14765,7 +14799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>1018</v>
       </c>
@@ -14795,7 +14829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>1020</v>
       </c>
@@ -14825,7 +14859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>1022</v>
       </c>
@@ -14852,7 +14886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>1026</v>
       </c>
@@ -14882,7 +14916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>1030</v>
       </c>
@@ -14912,7 +14946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>1034</v>
       </c>
@@ -14942,7 +14976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>1038</v>
       </c>
@@ -14972,7 +15006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>1042</v>
       </c>
@@ -15002,7 +15036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>1046</v>
       </c>
@@ -15032,7 +15066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>1049</v>
       </c>
@@ -15062,7 +15096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>1053</v>
       </c>
@@ -15092,7 +15126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>1057</v>
       </c>
@@ -15122,7 +15156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>1061</v>
       </c>
@@ -15152,7 +15186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>1065</v>
       </c>
@@ -15182,7 +15216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>1069</v>
       </c>
@@ -15212,7 +15246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1073</v>
       </c>
@@ -15242,7 +15276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1077</v>
       </c>
@@ -15269,7 +15303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1081</v>
       </c>
@@ -15299,7 +15333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1087</v>
       </c>
@@ -15329,7 +15363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1091</v>
       </c>
@@ -15359,7 +15393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1092</v>
       </c>
@@ -15389,7 +15423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1096</v>
       </c>
@@ -15419,7 +15453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1100</v>
       </c>
@@ -15446,7 +15480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1104</v>
       </c>
@@ -15473,7 +15507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1108</v>
       </c>
@@ -15500,7 +15534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1112</v>
       </c>
@@ -15513,8 +15547,9 @@
       <c r="D280" t="s">
         <v>1115</v>
       </c>
-      <c r="E280" t="s">
-        <v>626</v>
+      <c r="E280" t="str">
+        <f>G280</f>
+        <v>Benfeitorias e outros</v>
       </c>
       <c r="F280" t="s">
         <v>626</v>
@@ -15527,7 +15562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1116</v>
       </c>
@@ -15554,7 +15589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1120</v>
       </c>
@@ -15584,7 +15619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1125</v>
       </c>
@@ -15614,7 +15649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1129</v>
       </c>
@@ -15644,7 +15679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1132</v>
       </c>
@@ -15671,7 +15706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1136</v>
       </c>
@@ -15701,7 +15736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1140</v>
       </c>
@@ -15731,7 +15766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1144</v>
       </c>
@@ -15761,7 +15796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1148</v>
       </c>
@@ -15791,7 +15826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1152</v>
       </c>
@@ -15804,8 +15839,9 @@
       <c r="D290" t="s">
         <v>1155</v>
       </c>
-      <c r="E290" t="s">
-        <v>626</v>
+      <c r="E290" t="str">
+        <f>G290</f>
+        <v>Equipamentos</v>
       </c>
       <c r="F290" t="s">
         <v>626</v>
@@ -15818,7 +15854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1157</v>
       </c>
@@ -15848,7 +15884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1163</v>
       </c>
@@ -15878,7 +15914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1167</v>
       </c>
@@ -15908,7 +15944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1171</v>
       </c>
@@ -15938,7 +15974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1175</v>
       </c>
@@ -15968,7 +16004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1180</v>
       </c>
@@ -15995,7 +16031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1184</v>
       </c>
@@ -16022,7 +16058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1188</v>
       </c>
@@ -16049,7 +16085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1192</v>
       </c>
@@ -16079,7 +16115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1196</v>
       </c>
@@ -16109,7 +16145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1200</v>
       </c>
@@ -16139,7 +16175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1205</v>
       </c>
@@ -16169,7 +16205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1209</v>
       </c>
@@ -16199,7 +16235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1213</v>
       </c>
@@ -16226,7 +16262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1217</v>
       </c>
@@ -16256,7 +16292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1222</v>
       </c>
@@ -16283,7 +16319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1226</v>
       </c>
@@ -16310,7 +16346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1230</v>
       </c>
@@ -16340,7 +16376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1234</v>
       </c>
@@ -16367,7 +16403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1238</v>
       </c>
@@ -16397,7 +16433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1243</v>
       </c>
@@ -16424,7 +16460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>1247</v>
       </c>
@@ -16444,7 +16480,7 @@
         <v>384</v>
       </c>
       <c r="G312" t="s">
-        <v>653</v>
+        <v>2367</v>
       </c>
       <c r="H312">
         <f t="shared" si="4"/>
@@ -16454,7 +16490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>1251</v>
       </c>
@@ -16481,7 +16517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1255</v>
       </c>
@@ -16508,7 +16544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>1259</v>
       </c>
@@ -16535,7 +16571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>791</v>
       </c>
@@ -16565,7 +16601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>1263</v>
       </c>
@@ -16595,7 +16631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>1268</v>
       </c>
@@ -16625,7 +16661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1273</v>
       </c>
@@ -16655,7 +16691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>1277</v>
       </c>
@@ -16682,7 +16718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>1281</v>
       </c>
@@ -16709,7 +16745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>1285</v>
       </c>
@@ -16736,7 +16772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>1289</v>
       </c>
@@ -16763,7 +16799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>1293</v>
       </c>
@@ -16793,7 +16829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>1296</v>
       </c>
@@ -16823,7 +16859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>1300</v>
       </c>
@@ -16853,7 +16889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>1304</v>
       </c>
@@ -16880,7 +16916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>1308</v>
       </c>
@@ -16910,7 +16946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>1312</v>
       </c>
@@ -16937,7 +16973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1316</v>
       </c>
@@ -16967,7 +17003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>1320</v>
       </c>
@@ -16994,7 +17030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>1323</v>
       </c>
@@ -17021,7 +17057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>1327</v>
       </c>
@@ -17051,7 +17087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>1331</v>
       </c>
@@ -17081,7 +17117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>1334</v>
       </c>
@@ -17111,7 +17147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>1337</v>
       </c>
@@ -17141,7 +17177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>1340</v>
       </c>
@@ -17171,7 +17207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>1343</v>
       </c>
@@ -17198,7 +17234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>1346</v>
       </c>
@@ -17228,7 +17264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>1350</v>
       </c>
@@ -17255,7 +17291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1353</v>
       </c>
@@ -17282,7 +17318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>1357</v>
       </c>
@@ -17312,7 +17348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>1361</v>
       </c>
@@ -17342,7 +17378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>1363</v>
       </c>
@@ -17372,7 +17408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1366</v>
       </c>
@@ -17399,7 +17435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>1367</v>
       </c>
@@ -17429,7 +17465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>1371</v>
       </c>
@@ -17459,7 +17495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>1373</v>
       </c>
@@ -17486,7 +17522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1374</v>
       </c>
@@ -17516,7 +17552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>1378</v>
       </c>
@@ -17543,7 +17579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1382</v>
       </c>
@@ -17573,7 +17609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1387</v>
       </c>
@@ -17603,7 +17639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1391</v>
       </c>
@@ -17633,7 +17669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1395</v>
       </c>
@@ -17660,7 +17696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1399</v>
       </c>
@@ -17690,7 +17726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1403</v>
       </c>
@@ -17703,8 +17739,9 @@
       <c r="D356" t="s">
         <v>1406</v>
       </c>
-      <c r="E356" t="s">
-        <v>626</v>
+      <c r="E356" t="str">
+        <f>G356</f>
+        <v>Benfeitorias e outros</v>
       </c>
       <c r="F356" t="s">
         <v>626</v>
@@ -17717,7 +17754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1407</v>
       </c>
@@ -17744,7 +17781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1411</v>
       </c>
@@ -17774,7 +17811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1415</v>
       </c>
@@ -17804,7 +17841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1419</v>
       </c>
@@ -17831,7 +17868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1423</v>
       </c>
@@ -17861,7 +17898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1427</v>
       </c>
@@ -17888,7 +17925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1431</v>
       </c>
@@ -17918,7 +17955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1434</v>
       </c>
@@ -17948,7 +17985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1438</v>
       </c>
@@ -17978,7 +18015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1442</v>
       </c>
@@ -18008,7 +18045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1446</v>
       </c>
@@ -18035,7 +18072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1450</v>
       </c>
@@ -18065,7 +18102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1454</v>
       </c>
@@ -18095,7 +18132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1458</v>
       </c>
@@ -18122,7 +18159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1462</v>
       </c>
@@ -18152,7 +18189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1466</v>
       </c>
@@ -18179,7 +18216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1470</v>
       </c>
@@ -18206,7 +18243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1474</v>
       </c>
@@ -18233,7 +18270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1478</v>
       </c>
@@ -18263,7 +18300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1482</v>
       </c>
@@ -18290,7 +18327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1486</v>
       </c>
@@ -18317,7 +18354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1490</v>
       </c>
@@ -18344,7 +18381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1494</v>
       </c>
@@ -18371,7 +18408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1498</v>
       </c>
@@ -18398,7 +18435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1502</v>
       </c>
@@ -18425,7 +18462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1506</v>
       </c>
@@ -18455,7 +18492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1510</v>
       </c>
@@ -18485,7 +18522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1513</v>
       </c>
@@ -18515,7 +18552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1518</v>
       </c>
@@ -18545,7 +18582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1522</v>
       </c>
@@ -18575,7 +18612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1527</v>
       </c>
@@ -18605,7 +18642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1531</v>
       </c>
@@ -18635,7 +18672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1535</v>
       </c>
@@ -18665,7 +18702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1540</v>
       </c>
@@ -18695,7 +18732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1544</v>
       </c>
@@ -18722,7 +18759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1548</v>
       </c>
@@ -18749,7 +18786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1552</v>
       </c>
@@ -18776,7 +18813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1556</v>
       </c>
@@ -18803,7 +18840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1560</v>
       </c>
@@ -18833,7 +18870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1564</v>
       </c>
@@ -18863,7 +18900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1568</v>
       </c>
@@ -18876,8 +18913,9 @@
       <c r="D397" t="s">
         <v>1571</v>
       </c>
-      <c r="E397" t="s">
-        <v>626</v>
+      <c r="E397" t="str">
+        <f>G397</f>
+        <v>Equipamentos</v>
       </c>
       <c r="F397" t="s">
         <v>626</v>
@@ -18890,7 +18928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1572</v>
       </c>
@@ -18917,7 +18955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1576</v>
       </c>
@@ -18947,7 +18985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1580</v>
       </c>
@@ -18977,7 +19015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1584</v>
       </c>
@@ -19004,7 +19042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>1588</v>
       </c>
@@ -19034,7 +19072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1592</v>
       </c>
@@ -19064,7 +19102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>1596</v>
       </c>
@@ -19094,7 +19132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1600</v>
       </c>
@@ -19124,7 +19162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>1604</v>
       </c>
@@ -19151,7 +19189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1608</v>
       </c>
@@ -19178,7 +19216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1612</v>
       </c>
@@ -19208,7 +19246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1616</v>
       </c>
@@ -19221,8 +19259,9 @@
       <c r="D409" t="s">
         <v>1619</v>
       </c>
-      <c r="E409" t="s">
-        <v>626</v>
+      <c r="E409" t="str">
+        <f>G409</f>
+        <v>Benfeitorias e outros</v>
       </c>
       <c r="F409" t="s">
         <v>626</v>
@@ -19235,7 +19274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1620</v>
       </c>
@@ -19265,7 +19304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1624</v>
       </c>
@@ -19295,7 +19334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1628</v>
       </c>
@@ -19325,7 +19364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1632</v>
       </c>
@@ -19355,7 +19394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1636</v>
       </c>
@@ -19382,7 +19421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1640</v>
       </c>
@@ -19409,7 +19448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1643</v>
       </c>
@@ -19436,7 +19475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1647</v>
       </c>
@@ -19463,7 +19502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1651</v>
       </c>
@@ -19493,7 +19532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1656</v>
       </c>
@@ -19520,7 +19559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1659</v>
       </c>
@@ -19547,7 +19586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1663</v>
       </c>
@@ -19574,7 +19613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1667</v>
       </c>
@@ -19601,7 +19640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>1671</v>
       </c>
@@ -19628,7 +19667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>1675</v>
       </c>
@@ -19658,7 +19697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>1680</v>
       </c>
@@ -19688,7 +19727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>1684</v>
       </c>
@@ -19715,7 +19754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>1688</v>
       </c>
@@ -19745,7 +19784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1692</v>
       </c>
@@ -19775,7 +19814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1696</v>
       </c>
@@ -19802,7 +19841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>1700</v>
       </c>
@@ -19829,7 +19868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1704</v>
       </c>
@@ -19856,7 +19895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>1708</v>
       </c>
@@ -19883,7 +19922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>1711</v>
       </c>
@@ -19913,7 +19952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1715</v>
       </c>
@@ -19943,7 +19982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1719</v>
       </c>
@@ -19973,7 +20012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>1723</v>
       </c>
@@ -20000,7 +20039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>1727</v>
       </c>
@@ -20030,7 +20069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1731</v>
       </c>
@@ -20057,7 +20096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>1735</v>
       </c>
@@ -20087,7 +20126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>1739</v>
       </c>
@@ -20144,7 +20183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1747</v>
       </c>
@@ -20174,7 +20213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1751</v>
       </c>
@@ -20204,7 +20243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1755</v>
       </c>
@@ -20234,7 +20273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>1759</v>
       </c>
@@ -20261,7 +20300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>1763</v>
       </c>
@@ -20291,7 +20330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>1767</v>
       </c>
@@ -20304,8 +20343,9 @@
       <c r="D447" t="s">
         <v>1770</v>
       </c>
-      <c r="E447" t="s">
-        <v>626</v>
+      <c r="E447" t="str">
+        <f>G447</f>
+        <v>Software</v>
       </c>
       <c r="F447" t="s">
         <v>626</v>
@@ -20318,7 +20358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>1772</v>
       </c>
@@ -20348,7 +20388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>1776</v>
       </c>
@@ -20378,7 +20418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>1780</v>
       </c>
@@ -20408,7 +20448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>1784</v>
       </c>
@@ -20435,7 +20475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>1787</v>
       </c>
@@ -20462,7 +20502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>1791</v>
       </c>
@@ -20492,7 +20532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>1795</v>
       </c>
@@ -20522,7 +20562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>1799</v>
       </c>
@@ -20552,7 +20592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>1803</v>
       </c>
@@ -20582,7 +20622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>1807</v>
       </c>
@@ -20612,7 +20652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>1811</v>
       </c>
@@ -20642,7 +20682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>1815</v>
       </c>
@@ -20672,7 +20712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>1819</v>
       </c>
@@ -20699,7 +20739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>1823</v>
       </c>
@@ -20729,7 +20769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>1827</v>
       </c>
@@ -20759,7 +20799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>1831</v>
       </c>
@@ -20789,7 +20829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>1835</v>
       </c>
@@ -20819,7 +20859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>1839</v>
       </c>
@@ -20849,7 +20889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>1843</v>
       </c>
@@ -20876,7 +20916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>1847</v>
       </c>
@@ -20906,7 +20946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>1851</v>
       </c>
@@ -20936,7 +20976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>1855</v>
       </c>
@@ -20966,7 +21006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>1859</v>
       </c>
@@ -20996,7 +21036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>1863</v>
       </c>
@@ -21026,7 +21066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>1866</v>
       </c>
@@ -21056,7 +21096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>1870</v>
       </c>
@@ -21083,7 +21123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>1873</v>
       </c>
@@ -21110,7 +21150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>1877</v>
       </c>
@@ -21137,7 +21177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>1881</v>
       </c>
@@ -21164,7 +21204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>1885</v>
       </c>
@@ -21191,7 +21231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>1889</v>
       </c>
@@ -21221,7 +21261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>1893</v>
       </c>
@@ -21251,7 +21291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>1897</v>
       </c>
@@ -21281,7 +21321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>1901</v>
       </c>
@@ -21311,7 +21351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>1905</v>
       </c>
@@ -21341,7 +21381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>1909</v>
       </c>
@@ -21371,7 +21411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>1911</v>
       </c>
@@ -21401,7 +21441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>1913</v>
       </c>
@@ -21431,7 +21471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>1917</v>
       </c>
@@ -21461,7 +21501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>1921</v>
       </c>
@@ -21491,7 +21531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>1925</v>
       </c>
@@ -21521,7 +21561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>1929</v>
       </c>
@@ -21548,7 +21588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>1933</v>
       </c>
@@ -21578,7 +21618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>1937</v>
       </c>
@@ -21608,7 +21648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>1941</v>
       </c>
@@ -21638,7 +21678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>1945</v>
       </c>
@@ -21665,7 +21705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>1948</v>
       </c>
@@ -21695,7 +21735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>1952</v>
       </c>
@@ -21725,7 +21765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>1956</v>
       </c>
@@ -21755,7 +21795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>1960</v>
       </c>
@@ -21785,7 +21825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>1963</v>
       </c>
@@ -21815,7 +21855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>1964</v>
       </c>
@@ -21845,7 +21885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>1968</v>
       </c>
@@ -21875,7 +21915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>1971</v>
       </c>
@@ -21902,7 +21942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>1975</v>
       </c>
@@ -21932,7 +21972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>1979</v>
       </c>
@@ -21962,7 +22002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>1983</v>
       </c>
@@ -21989,7 +22029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>1987</v>
       </c>
@@ -22016,7 +22056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>1991</v>
       </c>
@@ -22046,7 +22086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>1995</v>
       </c>
@@ -22076,7 +22116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>1999</v>
       </c>
@@ -22106,7 +22146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>2002</v>
       </c>
@@ -22136,7 +22176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>2003</v>
       </c>
@@ -22166,7 +22206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>2007</v>
       </c>
@@ -22196,7 +22236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>2011</v>
       </c>
@@ -22226,7 +22266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>2015</v>
       </c>
@@ -22256,7 +22296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>2019</v>
       </c>
@@ -22286,7 +22326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>2023</v>
       </c>
@@ -22316,7 +22356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>2026</v>
       </c>
@@ -22346,7 +22386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>2030</v>
       </c>
@@ -22376,7 +22416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>2033</v>
       </c>
@@ -22406,7 +22446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>2034</v>
       </c>
@@ -22436,7 +22476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>2038</v>
       </c>
@@ -22466,7 +22506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>2042</v>
       </c>
@@ -22496,7 +22536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>2046</v>
       </c>
@@ -22526,7 +22566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>2048</v>
       </c>
@@ -22556,7 +22596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>2050</v>
       </c>
@@ -22586,7 +22626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>2054</v>
       </c>
@@ -22616,7 +22656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>2058</v>
       </c>
@@ -22646,7 +22686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>2062</v>
       </c>
@@ -22676,7 +22716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>2066</v>
       </c>
@@ -22706,7 +22746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>2068</v>
       </c>
@@ -22733,7 +22773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>2072</v>
       </c>
@@ -22760,7 +22800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>2076</v>
       </c>
@@ -22787,7 +22827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>2080</v>
       </c>
@@ -22814,7 +22854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>2084</v>
       </c>
@@ -22844,7 +22884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>2088</v>
       </c>
@@ -22874,7 +22914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>2091</v>
       </c>
@@ -22887,8 +22927,9 @@
       <c r="D535" t="s">
         <v>2094</v>
       </c>
-      <c r="E535" t="s">
-        <v>626</v>
+      <c r="E535" t="str">
+        <f>G535</f>
+        <v>Software</v>
       </c>
       <c r="F535" t="s">
         <v>626</v>
@@ -22901,7 +22942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>2095</v>
       </c>
@@ -22931,7 +22972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>2099</v>
       </c>
@@ -22958,7 +22999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>2102</v>
       </c>
@@ -22988,7 +23029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>2106</v>
       </c>
@@ -23015,7 +23056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>2109</v>
       </c>
@@ -23042,7 +23083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>2113</v>
       </c>
@@ -23069,7 +23110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>2117</v>
       </c>
@@ -23082,8 +23123,9 @@
       <c r="D542" t="s">
         <v>2120</v>
       </c>
-      <c r="E542" t="s">
-        <v>626</v>
+      <c r="E542" t="str">
+        <f t="shared" ref="E542:E544" si="9">G542</f>
+        <v>Software</v>
       </c>
       <c r="F542" t="s">
         <v>626</v>
@@ -23099,7 +23141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>2121</v>
       </c>
@@ -23112,8 +23154,9 @@
       <c r="D543" t="s">
         <v>2120</v>
       </c>
-      <c r="E543" t="s">
-        <v>626</v>
+      <c r="E543" t="str">
+        <f t="shared" si="9"/>
+        <v>Software</v>
       </c>
       <c r="F543" t="s">
         <v>626</v>
@@ -23126,7 +23169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>2124</v>
       </c>
@@ -23139,8 +23182,9 @@
       <c r="D544" t="s">
         <v>2127</v>
       </c>
-      <c r="E544" t="s">
-        <v>626</v>
+      <c r="E544" t="str">
+        <f t="shared" si="9"/>
+        <v>Software</v>
       </c>
       <c r="F544" t="s">
         <v>626</v>
@@ -23153,7 +23197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>2128</v>
       </c>
@@ -23183,7 +23227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>2132</v>
       </c>
@@ -23210,7 +23254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>2136</v>
       </c>
@@ -23240,7 +23284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>2139</v>
       </c>
@@ -23267,7 +23311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>2143</v>
       </c>
@@ -23297,7 +23341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>2147</v>
       </c>
@@ -23324,7 +23368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>2151</v>
       </c>
@@ -23354,7 +23398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>2155</v>
       </c>
@@ -23381,7 +23425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>2159</v>
       </c>
@@ -23411,7 +23455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>2163</v>
       </c>
@@ -23441,7 +23485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>2166</v>
       </c>
@@ -23468,7 +23512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>2170</v>
       </c>
@@ -23495,7 +23539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>2174</v>
       </c>
@@ -23522,7 +23566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>2178</v>
       </c>
@@ -23552,7 +23596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>2182</v>
       </c>
@@ -23582,7 +23626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>2186</v>
       </c>
@@ -23612,7 +23656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>2189</v>
       </c>
@@ -23639,7 +23683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>2193</v>
       </c>
@@ -23666,7 +23710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>2197</v>
       </c>
@@ -23696,7 +23740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>2201</v>
       </c>
@@ -23726,7 +23770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>2205</v>
       </c>
@@ -23756,7 +23800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>2209</v>
       </c>
@@ -23786,7 +23830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>2212</v>
       </c>
@@ -23816,7 +23860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>2213</v>
       </c>
@@ -23829,8 +23873,9 @@
       <c r="D568" t="s">
         <v>2216</v>
       </c>
-      <c r="E568" t="s">
-        <v>626</v>
+      <c r="E568" t="str">
+        <f>G568</f>
+        <v>Benfeitorias e outros</v>
       </c>
       <c r="F568" t="s">
         <v>626</v>
@@ -23843,7 +23888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>2217</v>
       </c>
@@ -23873,7 +23918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>2221</v>
       </c>
@@ -23903,7 +23948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>2225</v>
       </c>
@@ -23933,7 +23978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>2229</v>
       </c>
@@ -23963,7 +24008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>2233</v>
       </c>
@@ -23993,7 +24038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>2237</v>
       </c>
@@ -24020,7 +24065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>2241</v>
       </c>
@@ -24047,7 +24092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>2244</v>
       </c>
@@ -24074,7 +24119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>2247</v>
       </c>
@@ -24101,7 +24146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>2251</v>
       </c>
@@ -24124,11 +24169,11 @@
         <v>18</v>
       </c>
       <c r="H578">
-        <f t="shared" ref="H578:H621" si="9">COUNTIF(A:A,A578)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H578:H621" si="10">COUNTIF(A:A,A578)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="579" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>2255</v>
       </c>
@@ -24151,11 +24196,11 @@
         <v>18</v>
       </c>
       <c r="H579">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="580" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>2259</v>
       </c>
@@ -24178,11 +24223,11 @@
         <v>18</v>
       </c>
       <c r="H580">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="581" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>2262</v>
       </c>
@@ -24205,11 +24250,11 @@
         <v>18</v>
       </c>
       <c r="H581">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="582" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>2266</v>
       </c>
@@ -24232,11 +24277,11 @@
         <v>229</v>
       </c>
       <c r="H582">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="583" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>2270</v>
       </c>
@@ -24259,11 +24304,11 @@
         <v>18</v>
       </c>
       <c r="H583">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="584" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>2273</v>
       </c>
@@ -24286,14 +24331,14 @@
         <v>224</v>
       </c>
       <c r="H584">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="I584">
         <v>1</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>2277</v>
       </c>
@@ -24316,11 +24361,11 @@
         <v>18</v>
       </c>
       <c r="H585">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="586" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>2281</v>
       </c>
@@ -24343,11 +24388,11 @@
         <v>18</v>
       </c>
       <c r="H586">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="587" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>2285</v>
       </c>
@@ -24370,11 +24415,11 @@
         <v>18</v>
       </c>
       <c r="H587">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="588" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>2289</v>
       </c>
@@ -24383,7 +24428,7 @@
         <v>'4703013006</v>
       </c>
       <c r="C588" t="str">
-        <f t="shared" ref="C588:C631" si="10">SUBSTITUTE($A588,".","")</f>
+        <f t="shared" ref="C588:C636" si="11">SUBSTITUTE($A588,".","")</f>
         <v>4703013006</v>
       </c>
       <c r="D588" t="s">
@@ -24399,20 +24444,20 @@
         <v>479</v>
       </c>
       <c r="H588">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="589" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>2290</v>
       </c>
       <c r="B589" t="str">
-        <f t="shared" ref="B589:B593" si="11">"'"&amp;C589</f>
+        <f t="shared" ref="B589:B593" si="12">"'"&amp;C589</f>
         <v>'31010050160002</v>
       </c>
       <c r="C589" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>31010050160002</v>
       </c>
       <c r="D589" t="s">
@@ -24428,20 +24473,20 @@
         <v>18</v>
       </c>
       <c r="H589">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>2292</v>
       </c>
       <c r="B590" t="str">
+        <f t="shared" si="12"/>
+        <v>'31010050080003</v>
+      </c>
+      <c r="C590" t="str">
         <f t="shared" si="11"/>
-        <v>'31010050080003</v>
-      </c>
-      <c r="C590" t="str">
-        <f t="shared" si="10"/>
         <v>31010050080003</v>
       </c>
       <c r="D590" t="s">
@@ -24457,20 +24502,20 @@
         <v>18</v>
       </c>
       <c r="H590">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="591" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>2293</v>
       </c>
       <c r="B591" t="str">
+        <f t="shared" si="12"/>
+        <v>'31010050140001</v>
+      </c>
+      <c r="C591" t="str">
         <f t="shared" si="11"/>
-        <v>'31010050140001</v>
-      </c>
-      <c r="C591" t="str">
-        <f t="shared" si="10"/>
         <v>31010050140001</v>
       </c>
       <c r="D591" t="s">
@@ -24486,20 +24531,20 @@
         <v>18</v>
       </c>
       <c r="H591">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="592" spans="1:9" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>2295</v>
       </c>
       <c r="B592" t="str">
+        <f t="shared" si="12"/>
+        <v>'31010050120002</v>
+      </c>
+      <c r="C592" t="str">
         <f t="shared" si="11"/>
-        <v>'31010050120002</v>
-      </c>
-      <c r="C592" t="str">
-        <f t="shared" si="10"/>
         <v>31010050120002</v>
       </c>
       <c r="D592" t="s">
@@ -24515,20 +24560,20 @@
         <v>18</v>
       </c>
       <c r="H592">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="593" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>2296</v>
       </c>
       <c r="B593" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v>'3101005016</v>
+      </c>
+      <c r="C593" s="2" t="str">
         <f t="shared" si="11"/>
-        <v>'3101005016</v>
-      </c>
-      <c r="C593" s="2" t="str">
-        <f t="shared" si="10"/>
         <v>3101005016</v>
       </c>
       <c r="D593" t="s">
@@ -24544,20 +24589,20 @@
         <v>18</v>
       </c>
       <c r="H593">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="594" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="594" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>2297</v>
       </c>
       <c r="B594" s="2" t="str">
-        <f t="shared" ref="B594" si="12">"'"&amp;C594</f>
+        <f t="shared" ref="B594" si="13">"'"&amp;C594</f>
         <v>'31010050140002</v>
       </c>
       <c r="C594" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>31010050140002</v>
       </c>
       <c r="D594" t="s">
@@ -24573,20 +24618,20 @@
         <v>18</v>
       </c>
       <c r="H594">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="595" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>2299</v>
       </c>
       <c r="B595" s="2" t="str">
-        <f t="shared" ref="B595:B596" si="13">"'"&amp;C595</f>
+        <f t="shared" ref="B595:B596" si="14">"'"&amp;C595</f>
         <v>'4703002017</v>
       </c>
       <c r="C595" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4703002017</v>
       </c>
       <c r="D595" t="s">
@@ -24602,20 +24647,20 @@
         <v>1517</v>
       </c>
       <c r="H595">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="596" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>2300</v>
       </c>
       <c r="B596" s="2" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>'31010070060002</v>
       </c>
       <c r="C596" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>31010070060002</v>
       </c>
       <c r="D596" t="s">
@@ -24631,20 +24676,20 @@
         <v>18</v>
       </c>
       <c r="H596">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="597" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>2303</v>
       </c>
       <c r="B597" s="2" t="str">
-        <f t="shared" ref="B597:B601" si="14">"'"&amp;C597</f>
+        <f t="shared" ref="B597:B601" si="15">"'"&amp;C597</f>
         <v>'4710002015</v>
       </c>
       <c r="C597" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4710002015</v>
       </c>
       <c r="D597" t="s">
@@ -24660,20 +24705,20 @@
         <v>224</v>
       </c>
       <c r="H597">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="598" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>2305</v>
       </c>
       <c r="B598" s="2" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>'4703015017</v>
       </c>
       <c r="C598" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4703015017</v>
       </c>
       <c r="D598" t="s">
@@ -24689,20 +24734,20 @@
         <v>247</v>
       </c>
       <c r="H598">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="599" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>2307</v>
       </c>
       <c r="B599" s="2" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>'4710001007</v>
       </c>
       <c r="C599" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4710001007</v>
       </c>
       <c r="D599" t="s">
@@ -24718,20 +24763,20 @@
         <v>224</v>
       </c>
       <c r="H599">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>2309</v>
       </c>
       <c r="B600" s="2" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>'4703015019</v>
       </c>
       <c r="C600" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4703015019</v>
       </c>
       <c r="D600" t="s">
@@ -24747,20 +24792,20 @@
         <v>247</v>
       </c>
       <c r="H600">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="601" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A601" s="3" t="s">
         <v>2311</v>
       </c>
       <c r="B601" s="3" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>'31010050040004</v>
       </c>
       <c r="C601" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>31010050040004</v>
       </c>
       <c r="D601" s="3" t="s">
@@ -24776,20 +24821,20 @@
         <v>18</v>
       </c>
       <c r="H601" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A602" s="3" t="s">
         <v>2313</v>
       </c>
       <c r="B602" s="3" t="str">
-        <f t="shared" ref="B602:B606" si="15">"'"&amp;C602</f>
+        <f t="shared" ref="B602:B606" si="16">"'"&amp;C602</f>
         <v>'5101001112</v>
       </c>
       <c r="C602" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5101001112</v>
       </c>
       <c r="D602" s="3" t="s">
@@ -24805,20 +24850,20 @@
         <v>892</v>
       </c>
       <c r="H602" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="603" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A603" s="3" t="s">
         <v>2315</v>
       </c>
       <c r="B603" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>'5101001114</v>
       </c>
       <c r="C603" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5101001114</v>
       </c>
       <c r="D603" s="3" t="s">
@@ -24834,20 +24879,20 @@
         <v>892</v>
       </c>
       <c r="H603" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="604" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="604" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A604" s="3" t="s">
         <v>2316</v>
       </c>
       <c r="B604" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>'5101001116</v>
       </c>
       <c r="C604" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5101001116</v>
       </c>
       <c r="D604" s="3" t="s">
@@ -24863,20 +24908,20 @@
         <v>892</v>
       </c>
       <c r="H604" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="605" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A605" s="3" t="s">
         <v>2318</v>
       </c>
       <c r="B605" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>'5101001117</v>
       </c>
       <c r="C605" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5101001117</v>
       </c>
       <c r="D605" s="3" t="s">
@@ -24892,20 +24937,20 @@
         <v>892</v>
       </c>
       <c r="H605" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="606" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A606" s="3" t="s">
         <v>2320</v>
       </c>
       <c r="B606" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>'5101001119</v>
       </c>
       <c r="C606" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5101001119</v>
       </c>
       <c r="D606" s="3" t="s">
@@ -24921,20 +24966,20 @@
         <v>892</v>
       </c>
       <c r="H606" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="607" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="607" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A607" s="3" t="s">
         <v>2321</v>
       </c>
       <c r="B607" s="3" t="str">
-        <f t="shared" ref="B607:B608" si="16">"'"&amp;C607</f>
+        <f t="shared" ref="B607:B608" si="17">"'"&amp;C607</f>
         <v>'5101001120</v>
       </c>
       <c r="C607" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5101001120</v>
       </c>
       <c r="D607" s="3" t="s">
@@ -24950,20 +24995,20 @@
         <v>892</v>
       </c>
       <c r="H607" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="608" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A608" s="3" t="s">
         <v>2323</v>
       </c>
       <c r="B608" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>'5101001121</v>
       </c>
       <c r="C608" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5101001121</v>
       </c>
       <c r="D608" s="3" t="s">
@@ -24979,20 +25024,20 @@
         <v>892</v>
       </c>
       <c r="H608" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="609" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="609" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A609" s="3" t="s">
         <v>2325</v>
       </c>
       <c r="B609" s="3" t="str">
-        <f t="shared" ref="B609:B618" si="17">"'"&amp;C609</f>
+        <f t="shared" ref="B609:B618" si="18">"'"&amp;C609</f>
         <v>'51010010040010</v>
       </c>
       <c r="C609" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>51010010040010</v>
       </c>
       <c r="D609" s="3" t="s">
@@ -25008,20 +25053,20 @@
         <v>892</v>
       </c>
       <c r="H609" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="610" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="610" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A610" s="3" t="s">
         <v>2327</v>
       </c>
       <c r="B610" s="3" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>'4710001008</v>
       </c>
       <c r="C610" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4710001008</v>
       </c>
       <c r="D610" s="3" t="s">
@@ -25037,20 +25082,20 @@
         <v>224</v>
       </c>
       <c r="H610" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="611" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="611" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A611" s="3" t="s">
         <v>2329</v>
       </c>
       <c r="B611" s="3" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>'51010010030010</v>
       </c>
       <c r="C611" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>51010010030010</v>
       </c>
       <c r="D611" s="3" t="s">
@@ -25066,20 +25111,20 @@
         <v>892</v>
       </c>
       <c r="H611" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="612" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="612" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A612" s="3" t="s">
         <v>2331</v>
       </c>
       <c r="B612" s="3" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>'5101001113</v>
       </c>
       <c r="C612" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5101001113</v>
       </c>
       <c r="D612" s="3" t="s">
@@ -25095,20 +25140,20 @@
         <v>892</v>
       </c>
       <c r="H612" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="613" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="613" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A613" s="3" t="s">
         <v>2332</v>
       </c>
       <c r="B613" s="3" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>'51010010030011</v>
       </c>
       <c r="C613" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>51010010030011</v>
       </c>
       <c r="D613" s="3" t="s">
@@ -25124,20 +25169,20 @@
         <v>892</v>
       </c>
       <c r="H613" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="614" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A614" s="3" t="s">
         <v>2333</v>
       </c>
       <c r="B614" s="3" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>'5101001122</v>
       </c>
       <c r="C614" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5101001122</v>
       </c>
       <c r="D614" s="3" t="s">
@@ -25153,20 +25198,20 @@
         <v>892</v>
       </c>
       <c r="H614" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="615" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A615" s="3" t="s">
         <v>2334</v>
       </c>
       <c r="B615" s="3" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>'5101001125</v>
       </c>
       <c r="C615" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5101001125</v>
       </c>
       <c r="D615" s="3" t="s">
@@ -25182,20 +25227,20 @@
         <v>892</v>
       </c>
       <c r="H615" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="616" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="616" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A616" s="3" t="s">
         <v>2335</v>
       </c>
       <c r="B616" s="3" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>'5101001123</v>
       </c>
       <c r="C616" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5101001123</v>
       </c>
       <c r="D616" s="3" t="s">
@@ -25211,20 +25256,20 @@
         <v>892</v>
       </c>
       <c r="H616" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="617" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="617" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A617" s="3" t="s">
         <v>2336</v>
       </c>
       <c r="B617" s="3" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>'51010010030015</v>
       </c>
       <c r="C617" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>51010010030015</v>
       </c>
       <c r="D617" s="3" t="s">
@@ -25240,20 +25285,20 @@
         <v>892</v>
       </c>
       <c r="H617" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="618" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="618" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A618" s="3" t="s">
         <v>2337</v>
       </c>
       <c r="B618" s="3" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>'51010010040016</v>
       </c>
       <c r="C618" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>51010010040016</v>
       </c>
       <c r="D618" s="3" t="s">
@@ -25269,20 +25314,20 @@
         <v>892</v>
       </c>
       <c r="H618" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="619" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="619" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A619" s="3" t="s">
         <v>2339</v>
       </c>
       <c r="B619" s="3" t="str">
-        <f t="shared" ref="B619:B621" si="18">"'"&amp;C619</f>
+        <f t="shared" ref="B619:B621" si="19">"'"&amp;C619</f>
         <v>'51010010040011</v>
       </c>
       <c r="C619" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>51010010040011</v>
       </c>
       <c r="D619" s="3" t="s">
@@ -25298,20 +25343,20 @@
         <v>892</v>
       </c>
       <c r="H619" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="620" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="620" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A620" s="3" t="s">
         <v>2340</v>
       </c>
       <c r="B620" s="3" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>'5101001118</v>
       </c>
       <c r="C620" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5101001118</v>
       </c>
       <c r="D620" s="3" t="s">
@@ -25327,20 +25372,20 @@
         <v>892</v>
       </c>
       <c r="H620" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="621" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="621" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A621" s="3" t="s">
         <v>2341</v>
       </c>
       <c r="B621" s="3" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>'5101001124</v>
       </c>
       <c r="C621" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5101001124</v>
       </c>
       <c r="D621" s="3" t="s">
@@ -25356,20 +25401,20 @@
         <v>892</v>
       </c>
       <c r="H621" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="622" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="622" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A622" s="3" t="s">
         <v>2342</v>
       </c>
       <c r="B622" s="3" t="str">
-        <f t="shared" ref="B622:B628" si="19">"'"&amp;C622</f>
+        <f t="shared" ref="B622:B628" si="20">"'"&amp;C622</f>
         <v>'51010010040013</v>
       </c>
       <c r="C622" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>51010010040013</v>
       </c>
       <c r="D622" s="3" t="s">
@@ -25388,16 +25433,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="623" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A623" s="3" t="s">
         <v>2343</v>
       </c>
       <c r="B623" s="3" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>'51010010030013</v>
       </c>
       <c r="C623" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>51010010030013</v>
       </c>
       <c r="D623" s="3" t="s">
@@ -25416,16 +25461,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="624" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A624" s="3" t="s">
         <v>2344</v>
       </c>
       <c r="B624" s="3" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>'51010010040012</v>
       </c>
       <c r="C624" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>51010010040012</v>
       </c>
       <c r="D624" s="3" t="s">
@@ -25444,16 +25489,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="625" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A625" s="3" t="s">
         <v>2346</v>
       </c>
       <c r="B625" s="3" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>'51010010030012</v>
       </c>
       <c r="C625" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>51010010030012</v>
       </c>
       <c r="D625" s="3" t="s">
@@ -25472,16 +25517,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="626" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A626" s="3" t="s">
         <v>2348</v>
       </c>
       <c r="B626" s="3" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>'5101001102</v>
       </c>
       <c r="C626" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5101001102</v>
       </c>
       <c r="D626" s="3" t="s">
@@ -25500,16 +25545,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="627" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A627" s="3" t="s">
         <v>2349</v>
       </c>
       <c r="B627" s="3" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>'51010010030009</v>
       </c>
       <c r="C627" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>51010010030009</v>
       </c>
       <c r="D627" s="3" t="s">
@@ -25528,16 +25573,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A628" s="3" t="s">
         <v>2351</v>
       </c>
       <c r="B628" s="3" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>'51010010040009</v>
       </c>
       <c r="C628" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>51010010040009</v>
       </c>
       <c r="D628" s="3" t="s">
@@ -25561,11 +25606,11 @@
         <v>2353</v>
       </c>
       <c r="B629" s="3" t="str">
-        <f t="shared" ref="B629:B630" si="20">"'"&amp;C629</f>
+        <f t="shared" ref="B629:B630" si="21">"'"&amp;C629</f>
         <v>'4703001096</v>
       </c>
       <c r="C629" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4703001096</v>
       </c>
       <c r="D629" t="s">
@@ -25581,7 +25626,7 @@
         <v>653</v>
       </c>
       <c r="H629">
-        <f>COUNTIF(A:A,A629)</f>
+        <f t="shared" ref="H629:H636" si="22">COUNTIF(A:A,A629)</f>
         <v>1</v>
       </c>
     </row>
@@ -25590,11 +25635,11 @@
         <v>2354</v>
       </c>
       <c r="B630" s="3" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>'4703001097</v>
       </c>
       <c r="C630" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4703001097</v>
       </c>
       <c r="D630" t="s">
@@ -25610,20 +25655,20 @@
         <v>653</v>
       </c>
       <c r="H630">
-        <f>COUNTIF(A:A,A630)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="631" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>2357</v>
       </c>
       <c r="B631" s="3" t="str">
-        <f t="shared" ref="B631" si="21">"'"&amp;C631</f>
+        <f t="shared" ref="B631" si="23">"'"&amp;C631</f>
         <v>'3103005010</v>
       </c>
       <c r="C631" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3103005010</v>
       </c>
       <c r="D631" t="s">
@@ -25639,13 +25684,159 @@
         <v>2359</v>
       </c>
       <c r="H631">
-        <f>COUNTIF(A:A,A631)</f>
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="632" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
+      <c r="A632">
+        <v>4703015014</v>
+      </c>
+      <c r="B632" s="3" t="str">
+        <f t="shared" ref="B632:B635" si="24">"'"&amp;C632</f>
+        <v>'4703015014</v>
+      </c>
+      <c r="C632" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>4703015014</v>
+      </c>
+      <c r="D632" t="s">
+        <v>2360</v>
+      </c>
+      <c r="E632" t="s">
+        <v>229</v>
+      </c>
+      <c r="F632" t="s">
+        <v>246</v>
+      </c>
+      <c r="G632" t="s">
+        <v>247</v>
+      </c>
+      <c r="H632">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="633" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
+      <c r="A633">
+        <v>4710001011</v>
+      </c>
+      <c r="B633" s="3" t="str">
+        <f t="shared" si="24"/>
+        <v>'4710001011</v>
+      </c>
+      <c r="C633" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>4710001011</v>
+      </c>
+      <c r="D633" t="s">
+        <v>2361</v>
+      </c>
+      <c r="E633" t="s">
+        <v>224</v>
+      </c>
+      <c r="F633" t="s">
+        <v>224</v>
+      </c>
+      <c r="G633" t="s">
+        <v>224</v>
+      </c>
+      <c r="H633">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="634" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
+      <c r="A634" t="s">
+        <v>2362</v>
+      </c>
+      <c r="B634" s="3" t="str">
+        <f t="shared" si="24"/>
+        <v>'4703004009</v>
+      </c>
+      <c r="C634" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>4703004009</v>
+      </c>
+      <c r="D634" t="s">
+        <v>2363</v>
+      </c>
+      <c r="E634" t="s">
+        <v>785</v>
+      </c>
+      <c r="F634" t="s">
+        <v>837</v>
+      </c>
+      <c r="G634" t="s">
+        <v>1517</v>
+      </c>
+      <c r="H634">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="635" spans="1:8" ht="14.45" x14ac:dyDescent="0.25">
+      <c r="A635">
+        <v>3101005014</v>
+      </c>
+      <c r="B635" s="3" t="str">
+        <f t="shared" si="24"/>
+        <v>'3101005014</v>
+      </c>
+      <c r="C635" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>3101005014</v>
+      </c>
+      <c r="D635" t="s">
+        <v>2364</v>
+      </c>
+      <c r="E635" t="s">
+        <v>219</v>
+      </c>
+      <c r="F635" t="s">
+        <v>156</v>
+      </c>
+      <c r="G635" t="s">
+        <v>218</v>
+      </c>
+      <c r="H635">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="636" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A636" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B636" s="3" t="str">
+        <f t="shared" ref="B636" si="25">"'"&amp;C636</f>
+        <v>'4703001036</v>
+      </c>
+      <c r="C636" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>4703001036</v>
+      </c>
+      <c r="D636" s="4" t="s">
+        <v>2366</v>
+      </c>
+      <c r="E636" t="s">
+        <v>383</v>
+      </c>
+      <c r="F636" t="s">
+        <v>384</v>
+      </c>
+      <c r="G636" t="s">
+        <v>653</v>
+      </c>
+      <c r="H636">
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I631" xr:uid="{2CDEB827-A2B7-42BE-B86F-19DD993B7A8F}"/>
+  <autoFilter ref="A1:I636" xr:uid="{2CDEB827-A2B7-42BE-B86F-19DD993B7A8F}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -25885,15 +26076,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="59b07191-4ed6-434d-b6b8-e3b8eb6ea78b" xsi:nil="true"/>
@@ -25903,6 +26085,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25925,14 +26116,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3A0E5BD-6856-4BD8-86B7-A043200B4EB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13772D28-219C-4C8D-81A2-CE9297684FD4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -25941,4 +26124,12 @@
     <ds:schemaRef ds:uri="5aa39241-bd05-473c-b724-95e3c4460550"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3A0E5BD-6856-4BD8-86B7-A043200B4EB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>